--- a/artfynd/A 36127-2025 artfynd.xlsx
+++ b/artfynd/A 36127-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>79468529</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613894.4950220245</v>
+        <v>613894</v>
       </c>
       <c r="R2" t="n">
-        <v>6951583.796467147</v>
+        <v>6951584</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -801,42 +796,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119628855</v>
+        <v>119628859</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614000</v>
+        <v>613950</v>
       </c>
       <c r="R3" t="n">
-        <v>6951451</v>
+        <v>6951485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,42 +907,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119628859</v>
+        <v>119628855</v>
       </c>
       <c r="B4" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613950</v>
+        <v>614000</v>
       </c>
       <c r="R4" t="n">
-        <v>6951485</v>
+        <v>6951451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,12 +1021,7 @@
         <v>119628857</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36127-2025 artfynd.xlsx
+++ b/artfynd/A 36127-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79468529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628859</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628855</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,8 +1146,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628857</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>